--- a/data/trans_orig/IP05A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A01-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43308</t>
+          <t>42595</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>58286</t>
+          <t>57539</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>47,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>38323</t>
+          <t>38992</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>53531</t>
+          <t>53349</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86114</t>
+          <t>85674</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>107321</t>
+          <t>106819</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,35%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,57%</t>
+          <t>60,29%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>21275</t>
+          <t>21204</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34807</t>
+          <t>35646</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>24488</t>
+          <t>23769</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>38819</t>
+          <t>38417</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,7%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>48789</t>
+          <t>49530</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>68726</t>
+          <t>69509</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,23%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>7557</t>
+          <t>7634</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>18614</t>
+          <t>17387</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>5325</t>
+          <t>5510</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>14826</t>
+          <t>15145</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,13%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15045</t>
+          <t>15375</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29746</t>
+          <t>29029</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,38%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>182390</t>
+          <t>181379</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>214390</t>
+          <t>215002</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>43,66%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>216029</t>
+          <t>215594</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>250344</t>
+          <t>250640</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,69%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>408292</t>
+          <t>407704</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>454010</t>
+          <t>455321</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>45,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>50,95%</t>
+          <t>51,1%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>155774</t>
+          <t>155023</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>187686</t>
+          <t>187901</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>37,5%</t>
+          <t>37,32%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>45,18%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>177280</t>
+          <t>177788</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>212088</t>
+          <t>211651</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,59%</t>
+          <t>44,5%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1377,7 +1377,7 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>386978</t>
+          <t>386689</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,43%</t>
+          <t>43,4%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35530</t>
+          <t>35686</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56108</t>
+          <t>56912</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>13,51%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>39855</t>
+          <t>39646</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>61034</t>
+          <t>60786</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,83%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80137</t>
+          <t>81276</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>108616</t>
+          <t>109436</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>12,28%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>83411</t>
+          <t>83838</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>105073</t>
+          <t>104682</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>47,92%</t>
+          <t>48,16%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,14%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>75824</t>
+          <t>75526</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>95347</t>
+          <t>96031</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,95%</t>
+          <t>47,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,73%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>163679</t>
+          <t>164186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>194138</t>
+          <t>194820</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>49,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,64%</t>
         </is>
       </c>
     </row>
@@ -1758,12 +1758,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>51481</t>
+          <t>50681</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>71798</t>
+          <t>70444</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,12 +1773,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,12%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48181</t>
+          <t>47440</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>66987</t>
+          <t>67077</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>30,0%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>103845</t>
+          <t>104363</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>131589</t>
+          <t>133148</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>31,42%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>39,61%</t>
+          <t>40,08%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12556</t>
+          <t>13005</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>26529</t>
+          <t>26032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>14,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>9672</t>
+          <t>9798</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21623</t>
+          <t>21609</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25620</t>
+          <t>25078</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>43332</t>
+          <t>42466</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,04%</t>
+          <t>12,78%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>323385</t>
+          <t>323949</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>365850</t>
+          <t>366486</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,57%</t>
+          <t>47,65%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>343218</t>
+          <t>343571</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>385674</t>
+          <t>385864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>678868</t>
+          <t>679267</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>742927</t>
+          <t>736458</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,48%</t>
+          <t>48,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,05%</t>
+          <t>52,59%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>240528</t>
+          <t>240003</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>279749</t>
+          <t>280691</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,15%</t>
+          <t>41,29%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>263421</t>
+          <t>261434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>303591</t>
+          <t>302532</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>42,13%</t>
+          <t>41,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>511899</t>
+          <t>513804</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>570654</t>
+          <t>569087</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,55%</t>
+          <t>36,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,75%</t>
+          <t>40,64%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>63446</t>
+          <t>62918</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>89801</t>
+          <t>89690</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,19%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>62988</t>
+          <t>60857</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>88124</t>
+          <t>87455</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,74%</t>
+          <t>8,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>130968</t>
+          <t>131257</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>167793</t>
+          <t>168294</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>12,02%</t>
         </is>
       </c>
     </row>
@@ -2788,12 +2788,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>57945</t>
+          <t>57560</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>72167</t>
+          <t>72247</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2803,12 +2803,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>63,26%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>78,78%</t>
+          <t>78,87%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2823,12 +2823,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52332</t>
+          <t>52351</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>67017</t>
+          <t>66428</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2838,12 +2838,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,72%</t>
+          <t>60,74%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,75%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115245</t>
+          <t>115617</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135596</t>
+          <t>135662</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,82%</t>
+          <t>65,03%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,27%</t>
+          <t>76,3%</t>
         </is>
       </c>
     </row>
@@ -2901,12 +2901,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>14585</t>
+          <t>14726</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>28304</t>
+          <t>28155</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2916,12 +2916,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2936,12 +2936,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>13913</t>
+          <t>14931</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>27678</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2951,12 +2951,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>17,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>32,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32396</t>
+          <t>32102</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51607</t>
+          <t>51481</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>28,96%</t>
         </is>
       </c>
     </row>
@@ -3014,12 +3014,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2073</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9262</t>
+          <t>10011</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3029,12 +3029,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3049,12 +3049,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3133</t>
+          <t>3092</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10858</t>
+          <t>10426</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3064,12 +3064,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,6%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6118</t>
+          <t>6395</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16682</t>
+          <t>16989</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,38%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -3244,12 +3244,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>302367</t>
+          <t>302513</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>333739</t>
+          <t>334094</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3259,12 +3259,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,86%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,88%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3279,12 +3279,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>336951</t>
+          <t>336706</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>370757</t>
+          <t>369176</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3294,12 +3294,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,15%</t>
+          <t>68,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,98%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>649378</t>
+          <t>648885</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>694279</t>
+          <t>694856</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,34%</t>
+          <t>73,4%</t>
         </is>
       </c>
     </row>
@@ -3357,12 +3357,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>93535</t>
+          <t>92600</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>121020</t>
+          <t>121413</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3372,12 +3372,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>26,76%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>95693</t>
+          <t>97677</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>126651</t>
+          <t>128890</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3407,12 +3407,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>197854</t>
+          <t>196218</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>240027</t>
+          <t>238956</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>20,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>25,24%</t>
         </is>
       </c>
     </row>
@@ -3470,12 +3470,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>19056</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35215</t>
+          <t>35622</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3485,12 +3485,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,79%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3505,12 +3505,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21064</t>
+          <t>21391</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>39117</t>
+          <t>39439</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3520,12 +3520,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44252</t>
+          <t>44326</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>68217</t>
+          <t>69509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,34%</t>
         </is>
       </c>
     </row>
@@ -3700,12 +3700,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>95557</t>
+          <t>95863</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>116317</t>
+          <t>117506</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3715,12 +3715,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,47%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>69,73%</t>
+          <t>70,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>106450</t>
+          <t>106930</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>126932</t>
+          <t>127558</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,03%</t>
+          <t>62,31%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>73,96%</t>
+          <t>74,33%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209225</t>
+          <t>209571</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>237986</t>
+          <t>238401</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>61,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,44%</t>
         </is>
       </c>
     </row>
@@ -3813,12 +3813,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>33808</t>
+          <t>32903</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>52674</t>
+          <t>51355</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3828,12 +3828,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>19,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,58%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3848,12 +3848,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>37442</t>
+          <t>37018</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>56074</t>
+          <t>56221</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,82%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,67%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>75719</t>
+          <t>76152</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102744</t>
+          <t>102505</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,37%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,29%</t>
         </is>
       </c>
     </row>
@@ -3926,12 +3926,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12799</t>
+          <t>12085</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>25926</t>
+          <t>25388</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3941,12 +3941,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,24%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3961,12 +3961,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>4391</t>
+          <t>3865</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>14189</t>
+          <t>13176</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3976,12 +3976,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,27%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>19096</t>
+          <t>18700</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>34955</t>
+          <t>36189</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>10,69%</t>
         </is>
       </c>
     </row>
@@ -4156,12 +4156,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>469831</t>
+          <t>469710</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>510101</t>
+          <t>510833</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>66,1%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4191,12 +4191,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>510774</t>
+          <t>508169</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>549522</t>
+          <t>552360</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,9%</t>
+          <t>67,55%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,05%</t>
+          <t>73,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>993132</t>
+          <t>992257</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1050089</t>
+          <t>1051464</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,89%</t>
+          <t>67,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,78%</t>
+          <t>71,88%</t>
         </is>
       </c>
     </row>
@@ -4269,12 +4269,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>150928</t>
+          <t>150204</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>188598</t>
+          <t>188563</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>21,24%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>26,54%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4304,12 +4304,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>161649</t>
+          <t>158766</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>199151</t>
+          <t>198058</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,49%</t>
+          <t>21,11%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>323010</t>
+          <t>321574</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>377106</t>
+          <t>374501</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>21,98%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,78%</t>
+          <t>25,6%</t>
         </is>
       </c>
     </row>
@@ -4382,12 +4382,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>39385</t>
+          <t>38858</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>62589</t>
+          <t>61677</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4417,12 +4417,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>33362</t>
+          <t>33081</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54810</t>
+          <t>54095</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>76483</t>
+          <t>78398</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>109172</t>
+          <t>109227</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,47%</t>
         </is>
       </c>
     </row>
@@ -4843,12 +4843,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>36726</t>
+          <t>36261</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>47752</t>
+          <t>47477</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4858,12 +4858,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,85%</t>
+          <t>61,07%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>79,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4878,12 +4878,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>46941</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>58324</t>
+          <t>58006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4893,12 +4893,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>84,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85503</t>
+          <t>86957</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102737</t>
+          <t>102554</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>66,8%</t>
+          <t>67,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,27%</t>
+          <t>80,12%</t>
         </is>
       </c>
     </row>
@@ -4956,12 +4956,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>10191</t>
+          <t>10521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>20685</t>
+          <t>21117</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4971,12 +4971,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>17,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4991,12 +4991,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>16876</t>
+          <t>17446</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5006,12 +5006,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19781</t>
+          <t>19351</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35488</t>
+          <t>34264</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>26,77%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>605</t>
+          <t>609</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5189</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>1777</t>
+          <t>1852</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>8465</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3187</t>
+          <t>3001</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>10768</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -5299,12 +5299,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>325948</t>
+          <t>326389</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>357380</t>
+          <t>357290</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -5314,12 +5314,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,28%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>75,86%</t>
+          <t>75,84%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -5334,12 +5334,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>329204</t>
+          <t>329113</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>361617</t>
+          <t>361533</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -5349,12 +5349,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,36%</t>
+          <t>67,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,99%</t>
+          <t>73,97%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>665303</t>
+          <t>664557</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>710001</t>
+          <t>709638</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>73,93%</t>
         </is>
       </c>
     </row>
@@ -5412,12 +5412,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90236</t>
+          <t>90996</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119321</t>
+          <t>119212</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -5427,12 +5427,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,31%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,3%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -5447,12 +5447,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>98409</t>
+          <t>101366</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>129743</t>
+          <t>131562</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>26,92%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>199221</t>
+          <t>200238</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>242080</t>
+          <t>241015</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,76%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,22%</t>
+          <t>25,11%</t>
         </is>
       </c>
     </row>
@@ -5525,12 +5525,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>17189</t>
+          <t>17541</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>33154</t>
+          <t>32529</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5540,12 +5540,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,04%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5560,12 +5560,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>20317</t>
+          <t>20109</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>37946</t>
+          <t>36855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>41442</t>
+          <t>42351</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64787</t>
+          <t>64419</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,71%</t>
         </is>
       </c>
     </row>
@@ -5755,12 +5755,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>122532</t>
+          <t>122112</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>140105</t>
+          <t>140258</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5770,12 +5770,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>81,21%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5790,12 +5790,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>133052</t>
+          <t>132210</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152765</t>
+          <t>151762</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,96%</t>
+          <t>70,51%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>81,48%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>259399</t>
+          <t>260160</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286441</t>
+          <t>286758</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,02%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,52%</t>
+          <t>79,61%</t>
         </is>
       </c>
     </row>
@@ -5868,12 +5868,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>22294</t>
+          <t>22803</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>37785</t>
+          <t>38373</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5883,12 +5883,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26384</t>
+          <t>26808</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>44317</t>
+          <t>45407</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>23,64%</t>
+          <t>24,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>52457</t>
+          <t>51196</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>76724</t>
+          <t>75566</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,56%</t>
+          <t>14,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>20,98%</t>
         </is>
       </c>
     </row>
@@ -5981,12 +5981,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7184</t>
+          <t>6897</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18632</t>
+          <t>18618</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5996,12 +5996,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>3,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,79%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6016,12 +6016,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5301</t>
+          <t>5401</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>15786</t>
+          <t>16666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6031,12 +6031,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,42%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15232</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>31135</t>
+          <t>30354</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -6211,12 +6211,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>498193</t>
+          <t>497520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>535248</t>
+          <t>534620</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -6226,12 +6226,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>70,85%</t>
+          <t>70,75%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>76,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -6246,12 +6246,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>520398</t>
+          <t>520794</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>561319</t>
+          <t>561133</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,36%</t>
+          <t>75,34%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1027975</t>
+          <t>1031424</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1087717</t>
+          <t>1086688</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>70,99%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>75,12%</t>
+          <t>75,05%</t>
         </is>
       </c>
     </row>
@@ -6324,12 +6324,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>131182</t>
+          <t>131657</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167669</t>
+          <t>166608</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -6339,12 +6339,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>18,65%</t>
+          <t>18,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>23,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -6359,12 +6359,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>142154</t>
+          <t>141837</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>180062</t>
+          <t>179578</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -6374,12 +6374,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,11%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>285007</t>
+          <t>284855</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>337274</t>
+          <t>335323</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,29%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -6437,12 +6437,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>29050</t>
+          <t>28752</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>49561</t>
+          <t>48538</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -6452,12 +6452,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31427</t>
+          <t>32370</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>52274</t>
+          <t>53606</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6487,12 +6487,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>66719</t>
+          <t>67791</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95610</t>
+          <t>95949</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -6898,12 +6898,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>40541</t>
+          <t>39288</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>50128</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6913,12 +6913,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>91,68%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6933,12 +6933,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35442</t>
+          <t>35691</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49154</t>
+          <t>49907</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,16%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>79,28%</t>
+          <t>80,49%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6968,12 +6968,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>78961</t>
+          <t>79203</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97659</t>
+          <t>97979</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,67%</t>
+          <t>67,88%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,7%</t>
+          <t>83,97%</t>
         </is>
       </c>
     </row>
@@ -7011,12 +7011,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2602</t>
+          <t>2507</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10219</t>
+          <t>11411</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7026,12 +7026,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7046,12 +7046,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6862</t>
+          <t>6070</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19368</t>
+          <t>19158</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7061,12 +7061,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>11,07%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>31,24%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7081,12 +7081,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>11351</t>
+          <t>10670</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>25981</t>
+          <t>26080</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7096,12 +7096,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -7124,12 +7124,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>936</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7444</t>
+          <t>7335</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7139,12 +7139,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>13,61%</t>
+          <t>13,41%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7159,12 +7159,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3076</t>
+          <t>3196</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13417</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7174,12 +7174,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7194,12 +7194,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5802</t>
+          <t>5557</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16922</t>
+          <t>16805</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7209,12 +7209,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,5%</t>
+          <t>14,4%</t>
         </is>
       </c>
     </row>
@@ -7354,12 +7354,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>272924</t>
+          <t>278702</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>371715</t>
+          <t>372666</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7369,12 +7369,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>59,27%</t>
+          <t>60,52%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,72%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7389,12 +7389,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>411825</t>
+          <t>408895</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>443873</t>
+          <t>443742</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7404,12 +7404,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>79,15%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,92%</t>
+          <t>85,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7424,12 +7424,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>698687</t>
+          <t>685728</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>803806</t>
+          <t>802428</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7439,12 +7439,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>70,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,26%</t>
+          <t>82,12%</t>
         </is>
       </c>
     </row>
@@ -7467,12 +7467,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72199</t>
+          <t>72069</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>176435</t>
+          <t>170340</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7482,12 +7482,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>36,99%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7502,12 +7502,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51564</t>
+          <t>51672</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>80637</t>
+          <t>81227</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7517,12 +7517,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,61%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7537,12 +7537,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>134642</t>
+          <t>135589</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>243579</t>
+          <t>259659</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7552,12 +7552,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>26,57%</t>
         </is>
       </c>
     </row>
@@ -7580,12 +7580,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>9967</t>
+          <t>9968</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>24031</t>
+          <t>23563</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7600,7 +7600,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7615,12 +7615,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15276</t>
+          <t>15468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>33111</t>
+          <t>32384</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7630,12 +7630,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7650,12 +7650,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>27716</t>
+          <t>28981</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>50492</t>
+          <t>49834</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7665,12 +7665,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,1%</t>
         </is>
       </c>
     </row>
@@ -7810,12 +7810,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>111784</t>
+          <t>111183</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>128118</t>
+          <t>127807</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7825,12 +7825,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>74,75%</t>
+          <t>74,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>85,67%</t>
+          <t>85,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>129797</t>
+          <t>129479</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>151777</t>
+          <t>152529</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7860,12 +7860,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>71,16%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,21%</t>
+          <t>83,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>247485</t>
+          <t>248465</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275430</t>
+          <t>275008</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7895,12 +7895,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,55%</t>
+          <t>74,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,97%</t>
+          <t>82,84%</t>
         </is>
       </c>
     </row>
@@ -7923,12 +7923,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>13660</t>
+          <t>13490</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>28745</t>
+          <t>28250</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7938,12 +7938,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,02%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7958,12 +7958,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20250</t>
+          <t>20220</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41107</t>
+          <t>41109</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7973,7 +7973,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -7993,12 +7993,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37773</t>
+          <t>37510</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>63300</t>
+          <t>62031</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8008,12 +8008,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>18,69%</t>
         </is>
       </c>
     </row>
@@ -8036,12 +8036,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>5335</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>15677</t>
+          <t>15644</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8071,12 +8071,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6802</t>
+          <t>5951</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>19630</t>
+          <t>18298</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,03%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8106,12 +8106,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13567</t>
+          <t>13483</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30699</t>
+          <t>29814</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,09%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>8,98%</t>
         </is>
       </c>
     </row>
@@ -8266,12 +8266,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>443413</t>
+          <t>443232</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>539362</t>
+          <t>540857</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8281,12 +8281,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>81,14%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>591604</t>
+          <t>588423</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>632453</t>
+          <t>633833</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8316,12 +8316,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,74%</t>
+          <t>77,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,29%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1051606</t>
+          <t>1048628</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1159720</t>
+          <t>1160105</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8351,12 +8351,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,34%</t>
+          <t>81,37%</t>
         </is>
       </c>
     </row>
@@ -8379,12 +8379,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>96740</t>
+          <t>95807</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>196632</t>
+          <t>199282</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8394,12 +8394,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,55%</t>
+          <t>14,41%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,98%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88434</t>
+          <t>88234</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>125982</t>
+          <t>128318</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8429,12 +8429,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,62%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197853</t>
+          <t>197631</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>310250</t>
+          <t>311434</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8464,12 +8464,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,84%</t>
         </is>
       </c>
     </row>
@@ -8492,12 +8492,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>19373</t>
+          <t>19403</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>38084</t>
+          <t>37070</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8507,12 +8507,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8527,12 +8527,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32037</t>
+          <t>31035</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>54297</t>
+          <t>55013</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8542,12 +8542,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8562,12 +8562,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>55904</t>
+          <t>56694</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85471</t>
+          <t>85523</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8577,12 +8577,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP05A01-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP05A01-Estudios-trans_orig.xlsx
@@ -544,7 +544,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -555,7 +555,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -723,72 +723,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>46180</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>39694</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>53624</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>53,18%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>45,71%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>61,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>75</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>50798</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>42595</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>57539</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>43622</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>58297</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>56,23%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47,15%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>63,69%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>46180</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>38992</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>53349</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>53,18%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>44,9%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>64,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>85674</t>
+          <t>85501</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>106819</t>
+          <t>107159</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>48,35%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>60,29%</t>
+          <t>60,48%</t>
         </is>
       </c>
     </row>
@@ -836,72 +836,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31013</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>24267</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>37911</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>35,71%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>27,94%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>43,65%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>27700</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>21204</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>35646</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>21010</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>34901</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>30,66%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>23,47%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>39,46%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>31013</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>23769</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>38417</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>35,71%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>23,26%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>49530</t>
+          <t>48364</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>69509</t>
+          <t>69063</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>39,23%</t>
+          <t>38,98%</t>
         </is>
       </c>
     </row>
@@ -949,72 +949,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>9652</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>5566</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>15076</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>11,11%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>17,36%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>11843</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>7634</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>17387</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>7618</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>17976</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>13,11%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>8,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>19,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>9652</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>5510</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>15145</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>11,11%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>15375</t>
+          <t>15429</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>29029</t>
+          <t>29431</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>8,71%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,61%</t>
         </is>
       </c>
     </row>
@@ -1062,57 +1062,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>90340</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1179,72 +1179,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>232560</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>215106</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>249786</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>48,89%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>45,22%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>52,52%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>302</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>198902</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>181379</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>215002</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>181817</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>215058</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>47,88%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>43,66%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>51,76%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>232560</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>215594</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>250640</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>48,89%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>43,77%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>52,69%</t>
+          <t>51,77%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>407704</t>
+          <t>408188</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>455321</t>
+          <t>454488</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>51,1%</t>
+          <t>51,01%</t>
         </is>
       </c>
     </row>
@@ -1292,72 +1292,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>290</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>193749</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>177046</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>211282</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>40,73%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>37,22%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>44,42%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>171474</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>155023</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>187901</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>156327</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>188011</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>41,28%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>37,32%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>45,23%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>290</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>193749</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>177788</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>211651</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>40,73%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>45,26%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>341019</t>
+          <t>341454</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>386689</t>
+          <t>388378</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>38,27%</t>
+          <t>38,32%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>43,4%</t>
+          <t>43,59%</t>
         </is>
       </c>
     </row>
@@ -1405,72 +1405,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>49337</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>40015</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60689</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>10,37%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,41%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>12,76%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>67</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>45026</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>35686</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56912</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>35077</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>55748</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>10,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>8,59%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>13,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>49337</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>39646</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>60786</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>10,37%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,34%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>81276</t>
+          <t>79729</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>109436</t>
+          <t>109711</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>12,31%</t>
         </is>
       </c>
     </row>
@@ -1518,57 +1518,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475645</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475645</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475645</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>627</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>415401</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>415401</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>415401</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>475645</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>475645</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>475645</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1635,72 +1635,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>85986</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75615</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>96048</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>54,37%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>47,82%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>60,74%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>93998</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>83838</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>104682</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>82988</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>104492</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>54,0%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>48,16%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>60,14%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>85986</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>75526</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>96031</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>54,37%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>164186</t>
+          <t>165983</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>194820</t>
+          <t>194542</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>49,42%</t>
+          <t>49,96%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,56%</t>
         </is>
       </c>
     </row>
@@ -1748,72 +1748,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>57152</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>47352</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>67058</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>36,14%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>29,94%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>42,4%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>90</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>61272</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>50681</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>70444</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>51244</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>71618</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>35,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>29,12%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>40,47%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>85</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>57152</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>47440</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>67077</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>36,14%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>30,0%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>42,42%</t>
+          <t>41,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>104363</t>
+          <t>105357</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>133148</t>
+          <t>133527</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,42%</t>
+          <t>31,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,19%</t>
         </is>
       </c>
     </row>
@@ -1861,72 +1861,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>15000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>9820</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>21483</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>9,49%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>6,21%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>13,58%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>28</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18796</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>13005</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>26032</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12854</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>26853</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,8%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,47%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>14,96%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>15000</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>9798</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>21609</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>9,49%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>25078</t>
+          <t>25722</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>42466</t>
+          <t>42952</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>12,78%</t>
+          <t>12,93%</t>
         </is>
       </c>
     </row>
@@ -1974,57 +1974,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2091,72 +2091,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>550</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>364726</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>345355</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>385023</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>50,61%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>47,92%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>53,43%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>513</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>343698</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>323949</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>366486</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>324531</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>366182</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>50,56%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>47,65%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>53,91%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>550</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>364726</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>343571</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>385864</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>50,61%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>47,74%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>53,87%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>679267</t>
+          <t>678232</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>736458</t>
+          <t>738443</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>48,5%</t>
+          <t>48,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>52,59%</t>
+          <t>52,73%</t>
         </is>
       </c>
     </row>
@@ -2204,72 +2204,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>421</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>281913</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>261012</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>301881</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>39,12%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>36,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>41,89%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>390</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>260445</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>240003</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>280691</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>239222</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>278985</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>38,31%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>35,3%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>41,29%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>421</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>281913</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>261434</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>302532</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>39,12%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>41,98%</t>
+          <t>41,04%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>513804</t>
+          <t>513629</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>569087</t>
+          <t>570376</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>36,69%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>40,64%</t>
+          <t>40,73%</t>
         </is>
       </c>
     </row>
@@ -2317,72 +2317,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>73989</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>61774</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>87010</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>10,27%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>8,57%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>12,07%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>113</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>75665</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>62918</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>89690</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>62913</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>90838</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>11,13%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>9,26%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>13,19%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>73989</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>60857</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>87455</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>10,27%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>12,14%</t>
+          <t>13,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>131257</t>
+          <t>129972</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>168294</t>
+          <t>166728</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>11,91%</t>
         </is>
       </c>
     </row>
@@ -2430,57 +2430,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1083</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>720628</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>720628</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>720628</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1016</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>679808</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>679808</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>679808</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1083</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>720628</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>720628</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>720628</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2599,7 +2599,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2610,7 +2610,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2778,72 +2778,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>59772</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>52384</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>66542</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>69,35%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>60,78%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>77,2%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>96</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>65496</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>57560</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>72247</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>56631</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>71853</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>71,5%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>62,84%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>78,87%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>59772</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>52351</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>66428</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>69,35%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>60,74%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>77,07%</t>
+          <t>78,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2858,12 +2858,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>115617</t>
+          <t>115018</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135662</t>
+          <t>134142</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2873,12 +2873,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>65,03%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>76,3%</t>
+          <t>75,45%</t>
         </is>
       </c>
     </row>
@@ -2891,72 +2891,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>20514</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>14329</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>27287</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>23,8%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>16,62%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>31,66%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>30</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>21137</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>14726</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>28155</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>15283</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>29293</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>23,08%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>16,08%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>30,74%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>20514</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>14931</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>28264</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>23,8%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>17,32%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>32,79%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2971,12 +2971,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>32102</t>
+          <t>32870</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>51481</t>
+          <t>51620</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2986,12 +2986,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>18,49%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,96%</t>
+          <t>29,03%</t>
         </is>
       </c>
     </row>
@@ -3004,72 +3004,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>5906</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>3101</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>10521</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,85%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>12,21%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>4968</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2132</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>10011</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2165</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>9890</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>5,42%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>10,93%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>5906</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>3092</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>10426</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3084,12 +3084,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>6395</t>
+          <t>6746</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>17631</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3099,12 +3099,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,92%</t>
         </is>
       </c>
     </row>
@@ -3117,57 +3117,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>86192</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>91601</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>121</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>86192</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -3234,72 +3234,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>507</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>353580</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>338035</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>369321</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>71,51%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>68,37%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,69%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>463</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>318976</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>302513</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>334094</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>301862</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>333492</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>70,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>66,9%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>73,88%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>507</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>353580</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>336706</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>369176</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>71,51%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>74,66%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3314,12 +3314,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>648885</t>
+          <t>648752</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>694856</t>
+          <t>695169</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3329,12 +3329,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>68,54%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,4%</t>
+          <t>73,43%</t>
         </is>
       </c>
     </row>
@@ -3347,72 +3347,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>112095</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>98332</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>127373</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>22,67%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>19,89%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>25,76%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>153</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>106821</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>92600</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>121413</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>93384</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>122177</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>23,62%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>20,48%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>26,85%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>112095</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>97677</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>128890</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>22,67%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>20,65%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>196218</t>
+          <t>199761</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>238956</t>
+          <t>242701</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3442,12 +3442,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,73%</t>
+          <t>21,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,24%</t>
+          <t>25,64%</t>
         </is>
       </c>
     </row>
@@ -3460,72 +3460,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>28771</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20930</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>37771</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,82%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,23%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,64%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>26412</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>19056</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>35622</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>19624</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>35825</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,84%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>4,21%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>7,88%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>28771</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>21391</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>39439</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3540,12 +3540,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>44326</t>
+          <t>44226</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>69509</t>
+          <t>67321</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3555,12 +3555,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -3573,57 +3573,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>708</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>494446</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>655</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>452210</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>494446</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3690,72 +3690,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>117482</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>105845</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>127244</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>68,45%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>61,67%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>74,14%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>151</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>106453</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>95863</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>117506</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>95806</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>116819</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>63,82%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>57,47%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>70,44%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>166</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>117482</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>106930</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>127558</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>68,45%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>62,31%</t>
+          <t>57,43%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>70,03%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -3770,12 +3770,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>209571</t>
+          <t>210230</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>238401</t>
+          <t>238135</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -3785,12 +3785,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>61,92%</t>
+          <t>62,12%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,36%</t>
         </is>
       </c>
     </row>
@@ -3803,72 +3803,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>46228</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>36599</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>55921</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>26,94%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>21,33%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>32,58%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>60</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>42029</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>32903</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>51355</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>33265</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>52082</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>25,2%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>30,79%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>46228</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>37018</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>56221</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>26,94%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>21,57%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>32,76%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3883,12 +3883,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>76152</t>
+          <t>75302</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>102505</t>
+          <t>101475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3898,12 +3898,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>22,5%</t>
+          <t>22,25%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>30,29%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -3916,72 +3916,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7911</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4216</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>14120</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>4,61%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,46%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,23%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>18330</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>12085</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>25388</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>12603</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>26690</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>10,99%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>7,24%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>15,22%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>7911</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>3865</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>13176</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>4,61%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3996,12 +3996,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18700</t>
+          <t>18639</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36189</t>
+          <t>34850</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,53%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>10,69%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -4029,57 +4029,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>171621</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>171621</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>171621</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>236</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>166812</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>171621</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>171621</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>171621</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -4146,72 +4146,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>756</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>530834</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>510027</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>551817</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>70,57%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>67,8%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>73,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>710</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>490926</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>469710</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>510833</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>471766</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>510558</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>69,08%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>66,1%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>71,89%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>756</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>530834</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>508169</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>552360</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>70,57%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>67,55%</t>
+          <t>66,39%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>73,43%</t>
+          <t>71,85%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4226,12 +4226,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>992257</t>
+          <t>989777</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1051464</t>
+          <t>1049604</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4241,12 +4241,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>67,83%</t>
+          <t>67,66%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,75%</t>
         </is>
       </c>
     </row>
@@ -4259,72 +4259,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>178837</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>158853</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>198492</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>23,77%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>21,12%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>26,39%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>243</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>169987</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>150204</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>188563</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>151604</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>189327</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>23,92%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>21,14%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>26,53%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>256</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>178837</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>158766</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>198058</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>23,77%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>21,11%</t>
+          <t>21,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>26,33%</t>
+          <t>26,64%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4339,12 +4339,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>321574</t>
+          <t>323498</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>374501</t>
+          <t>379696</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>21,98%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>25,6%</t>
+          <t>25,96%</t>
         </is>
       </c>
     </row>
@@ -4372,72 +4372,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>42587</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>33149</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>54775</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,41%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,28%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>71</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>49709</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>38858</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>61677</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>39077</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>60548</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>7,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>5,47%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>42587</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>33081</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>54095</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>8,52%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4452,12 +4452,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>78398</t>
+          <t>78131</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>109227</t>
+          <t>109185</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>7,46%</t>
         </is>
       </c>
     </row>
@@ -4485,57 +4485,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1072</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>752258</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>752258</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>752258</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1024</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>710623</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>710623</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>710623</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1072</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>752258</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>752258</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>752258</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -4654,7 +4654,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -4665,7 +4665,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -4833,72 +4833,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>52527</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>45981</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>57873</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>76,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>67,01%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>84,35%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>63</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>42477</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>36261</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>47477</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>36479</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>47749</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>71,54%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>61,07%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>79,96%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>52527</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>46069</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>58006</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>76,55%</t>
-        </is>
-      </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>67,14%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4913,12 +4913,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>86957</t>
+          <t>85710</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>102554</t>
+          <t>101264</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4928,12 +4928,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,94%</t>
+          <t>66,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>80,12%</t>
+          <t>79,12%</t>
         </is>
       </c>
     </row>
@@ -4946,72 +4946,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>11542</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>7089</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>17874</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>16,82%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>10,33%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>26,05%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>15038</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>10521</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21117</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>10011</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>21109</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>25,33%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>17,72%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>35,56%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>11542</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>6901</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>17446</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>16,82%</t>
-        </is>
-      </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>35,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5026,12 +5026,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>19351</t>
+          <t>20028</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>34264</t>
+          <t>35200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5041,12 +5041,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>26,77%</t>
+          <t>27,5%</t>
         </is>
       </c>
     </row>
@@ -5059,72 +5059,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>4544</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>1788</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>9095</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>6,62%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>2,61%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>13,25%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>1863</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>609</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>5189</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>605</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>4930</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
         <is>
           <t>3,14%</t>
         </is>
       </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,03%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>8,74%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>4544</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>1852</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>8465</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>6,62%</t>
-        </is>
-      </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>8,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>3001</t>
+          <t>2988</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10768</t>
+          <t>11532</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,33%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,01%</t>
         </is>
       </c>
     </row>
@@ -5172,57 +5172,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5289,72 +5289,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>346155</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>329819</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>362774</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>70,83%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>67,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>74,23%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>518</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>342806</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>326389</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>357290</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>326159</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>359029</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>72,76%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>69,28%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,84%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>489</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>346155</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>329113</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>361533</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>70,83%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>69,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>73,97%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -5369,12 +5369,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>664557</t>
+          <t>666639</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>709638</t>
+          <t>713100</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -5384,12 +5384,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>69,23%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>73,93%</t>
+          <t>74,29%</t>
         </is>
       </c>
     </row>
@@ -5402,72 +5402,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>114933</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>98227</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>130298</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>23,52%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20,1%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>26,66%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>159</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>104061</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>90996</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>119212</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>89542</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>119924</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>22,09%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>19,31%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>25,3%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>165</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>114933</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>101366</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>131562</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>23,52%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -5482,12 +5482,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>200238</t>
+          <t>198717</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>241015</t>
+          <t>240782</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,09%</t>
         </is>
       </c>
     </row>
@@ -5515,72 +5515,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>27647</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>20404</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>36981</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>5,66%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4,17%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>7,57%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>24255</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>17541</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>32529</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>17127</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>33019</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>5,15%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,72%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>27647</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>20109</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>36855</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>5,66%</t>
-        </is>
-      </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,54%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5595,12 +5595,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>42351</t>
+          <t>42007</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>64419</t>
+          <t>64381</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5610,7 +5610,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,41%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -5628,57 +5628,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>713</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>471123</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
         <is>
           <t>471123</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>471123</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5745,72 +5745,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>142775</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>133326</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>152109</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>76,15%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>71,11%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>81,13%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>195</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>131307</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>122112</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>140258</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>120231</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>139690</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
         <is>
           <t>76,03%</t>
         </is>
       </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>70,71%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>81,21%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>207</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>142775</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>132210</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>151762</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>76,15%</t>
-        </is>
-      </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,51%</t>
+          <t>69,62%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>80,94%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5825,12 +5825,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>260160</t>
+          <t>260607</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>286758</t>
+          <t>288288</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>72,35%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>79,61%</t>
+          <t>80,04%</t>
         </is>
       </c>
     </row>
@@ -5858,72 +5858,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>34961</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>26390</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>43734</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>18,65%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>14,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>23,33%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>29444</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>22803</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>38373</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>22480</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>39192</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>17,05%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>13,2%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>22,22%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>51</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>34961</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>26808</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>45407</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>18,65%</t>
-        </is>
-      </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>13,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,22%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5938,12 +5938,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>51196</t>
+          <t>53306</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>75566</t>
+          <t>77121</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>21,41%</t>
         </is>
       </c>
     </row>
@@ -5971,72 +5971,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9759</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5169</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>15508</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,21%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,76%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>8,27%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>11952</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>6897</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>18618</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>6977</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>18186</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>6,92%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,99%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,78%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>9759</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>5401</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>16666</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>5,21%</t>
-        </is>
-      </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6051,12 +6051,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>15043</t>
+          <t>14680</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>30354</t>
+          <t>31202</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6066,12 +6066,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,66%</t>
         </is>
       </c>
     </row>
@@ -6084,57 +6084,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6201,72 +6201,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>770</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>541457</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>522434</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>562709</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>72,69%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>70,14%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>75,55%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>776</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
         <is>
           <t>516591</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>497520</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>534620</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>496615</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>534105</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>73,46%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>70,75%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>76,03%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>770</t>
-        </is>
-      </c>
-      <c r="K16" s="2" t="inlineStr">
-        <is>
-          <t>541457</t>
-        </is>
-      </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>520794</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>561133</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>72,69%</t>
-        </is>
-      </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>75,34%</t>
+          <t>75,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -6281,12 +6281,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1031424</t>
+          <t>1032308</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1086688</t>
+          <t>1086734</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
@@ -6314,72 +6314,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>161437</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>143182</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>179758</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>21,67%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>19,22%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>24,13%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>228</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
         <is>
           <t>148543</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>131657</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>166608</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>132147</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>166316</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>21,12%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>18,72%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>23,69%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>161437</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>141837</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>179578</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>24,11%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -6394,12 +6394,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>284855</t>
+          <t>286820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>335323</t>
+          <t>338577</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>19,67%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>23,38%</t>
         </is>
       </c>
     </row>
@@ -6427,72 +6427,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>41950</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>31662</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>52973</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,25%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,11%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>56</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="K18" s="2" t="inlineStr">
         <is>
           <t>38070</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>28752</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>48538</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>29891</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>49649</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
         <is>
           <t>5,41%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>4,09%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>6,9%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>61</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>41950</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>32370</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>53606</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>5,63%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>67791</t>
+          <t>65571</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>95949</t>
+          <t>93608</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6522,12 +6522,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,53%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>6,46%</t>
         </is>
       </c>
     </row>
@@ -6540,57 +6540,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>1060</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="K19" s="2" t="inlineStr">
         <is>
           <t>703204</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="L19" s="2" t="inlineStr">
         <is>
           <t>703204</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="M19" s="2" t="inlineStr">
         <is>
           <t>703204</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6709,7 +6709,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -6720,7 +6720,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -6888,72 +6888,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>62</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>39904</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>33208</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>46146</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>70,34%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>58,53%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>81,34%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>53</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>45961</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>39288</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>50029</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>84,06%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>71,85%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>91,5%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>62</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>43272</t>
+          <t>37072</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>35691</t>
+          <t>31660</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>49907</t>
+          <t>40947</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>69,79%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,49%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6963,32 +6963,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>89232</t>
+          <t>76976</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>79203</t>
+          <t>68468</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>97979</t>
+          <t>84055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>67,88%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>81,22%</t>
         </is>
       </c>
     </row>
@@ -7001,72 +7001,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>9861</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>5200</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>16467</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>17,38%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>9,17%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>29,03%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>5653</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2507</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>11411</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>10,34%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>4,59%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>20,87%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11664</t>
+          <t>6107</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>6070</t>
+          <t>3107</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>10721</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7076,32 +7076,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>17316</t>
+          <t>15969</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>10670</t>
+          <t>10333</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>26080</t>
+          <t>23520</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>14,84%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,73%</t>
         </is>
       </c>
     </row>
@@ -7114,72 +7114,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>6966</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2934</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>12429</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>12,28%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>5,17%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>21,91%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>3065</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>936</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>7335</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>5,6%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,71%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>13,41%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>7069</t>
+          <t>3579</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>3196</t>
+          <t>1333</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13423</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>17,75%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7189,32 +7189,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>10133</t>
+          <t>10545</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>5557</t>
+          <t>5539</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>16805</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>8,68%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,4%</t>
+          <t>17,18%</t>
         </is>
       </c>
     </row>
@@ -7227,57 +7227,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>56732</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>69</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>54678</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>62004</t>
+          <t>46758</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7302,17 +7302,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>116682</t>
+          <t>103490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7344,72 +7344,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>540</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>389978</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>373332</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>405015</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>81,98%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>78,48%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>85,14%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>519</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>345560</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>278702</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>372666</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>75,04%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>60,52%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>80,92%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>540</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>427629</t>
+          <t>339065</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>408895</t>
+          <t>323223</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>443742</t>
+          <t>353115</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>82,77%</t>
+          <t>78,41%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>79,15%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>85,89%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7419,32 +7419,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>773188</t>
+          <t>729043</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>685728</t>
+          <t>707508</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>802428</t>
+          <t>750922</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>79,13%</t>
+          <t>80,28%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>77,91%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,69%</t>
         </is>
       </c>
     </row>
@@ -7457,72 +7457,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>62434</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>49579</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>76308</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>13,13%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>10,42%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>16,04%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>101</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>99446</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>72069</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>170340</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>21,59%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>15,65%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>36,99%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>65480</t>
+          <t>77291</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>51672</t>
+          <t>64229</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>81227</t>
+          <t>92545</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>12,67%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7532,32 +7532,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>164926</t>
+          <t>139725</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>135589</t>
+          <t>119677</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>259659</t>
+          <t>159197</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>16,88%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,18%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,57%</t>
+          <t>17,53%</t>
         </is>
       </c>
     </row>
@@ -7570,72 +7570,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>23266</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>15297</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>33027</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>3,22%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>6,94%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>15504</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>9968</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>23563</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>3,37%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2,16%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>5,12%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>23511</t>
+          <t>16092</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>15468</t>
+          <t>10251</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>32384</t>
+          <t>23952</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7645,32 +7645,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>39015</t>
+          <t>39358</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>28981</t>
+          <t>29973</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>49834</t>
+          <t>50813</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -7683,57 +7683,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>656</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>475678</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>643</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>460510</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>656</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>516619</t>
+          <t>432448</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7758,17 +7758,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>977129</t>
+          <t>908126</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7800,72 +7800,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>132185</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>121670</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>141011</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>78,93%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>72,66%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>84,2%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>120499</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>111183</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>127807</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>80,57%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>74,34%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>85,46%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>189</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>142422</t>
+          <t>121122</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>129479</t>
+          <t>112967</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>152529</t>
+          <t>128703</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>80,76%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>70,98%</t>
+          <t>75,32%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>83,62%</t>
+          <t>85,82%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7875,32 +7875,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>262922</t>
+          <t>253306</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>248465</t>
+          <t>240923</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>275008</t>
+          <t>264539</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,8%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>74,85%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>82,84%</t>
+          <t>83,34%</t>
         </is>
       </c>
     </row>
@@ -7913,72 +7913,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>25686</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>18470</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>35526</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>15,34%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>11,03%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>21,21%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>29</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>19934</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>13490</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>28250</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>13,33%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>9,02%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>28841</t>
+          <t>19794</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>20220</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>41109</t>
+          <t>27051</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,54%</t>
+          <t>18,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7988,32 +7988,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>48776</t>
+          <t>45480</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>37510</t>
+          <t>35267</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>62031</t>
+          <t>56531</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,33%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>11,3%</t>
+          <t>11,11%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,81%</t>
         </is>
       </c>
     </row>
@@ -8026,72 +8026,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>9592</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>5072</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>16219</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>5,73%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>9,69%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>9117</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>5141</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>15644</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>6,1%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3,44%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>10,46%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>11142</t>
+          <t>9060</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5951</t>
+          <t>4987</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>18298</t>
+          <t>15236</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8101,32 +8101,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>20259</t>
+          <t>18651</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>13483</t>
+          <t>12585</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>29814</t>
+          <t>26683</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>6,1%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -8139,57 +8139,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>167462</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>230</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>149551</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>237</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>182405</t>
+          <t>149976</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8214,17 +8214,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>317438</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8256,72 +8256,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>791</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>562067</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>541685</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>581382</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>80,31%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>77,4%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>83,07%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>760</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>512019</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>443232</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>540857</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>77,03%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>66,68%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>81,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>791</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>613322</t>
+          <t>497259</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>588423</t>
+          <t>476255</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>633833</t>
+          <t>512808</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>79,03%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>77,32%</t>
+          <t>75,69%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8331,32 +8331,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1125342</t>
+          <t>1059326</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>1048628</t>
+          <t>1029987</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>1160105</t>
+          <t>1086678</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>78,93%</t>
+          <t>79,71%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>73,55%</t>
+          <t>77,5%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -8369,72 +8369,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>97981</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>81718</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>117537</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>14,0%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>11,68%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>16,79%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>141</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>125033</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>95807</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>199282</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>18,81%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>14,41%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>29,98%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>131</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>105984</t>
+          <t>103193</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>88234</t>
+          <t>88121</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>128318</t>
+          <t>122179</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>16,4%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>14,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8444,32 +8444,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>231018</t>
+          <t>201174</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>197631</t>
+          <t>178554</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>311434</t>
+          <t>227435</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,14%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>17,11%</t>
         </is>
       </c>
     </row>
@@ -8482,72 +8482,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>39824</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>29812</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>52573</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>5,69%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>4,26%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>7,51%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>27686</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>19403</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>37070</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>4,16%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>2,92%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>54</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>41722</t>
+          <t>28730</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31035</t>
+          <t>21239</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>55013</t>
+          <t>39034</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,48%</t>
+          <t>4,57%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>7,23%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8557,32 +8557,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>69408</t>
+          <t>68554</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>56694</t>
+          <t>56069</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>85523</t>
+          <t>83326</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -8595,57 +8595,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>976</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>699872</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>942</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>664738</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>976</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>761028</t>
+          <t>629182</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8670,17 +8670,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1425767</t>
+          <t>1329054</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
